--- a/pregenereated_results/s2/att_iptw_gee_IPTW_GEE_manager_efficacy_index.xlsx
+++ b/pregenereated_results/s2/att_iptw_gee_IPTW_GEE_manager_efficacy_index.xlsx
@@ -1467,16 +1467,16 @@
         <v>2.236944464107626</v>
       </c>
       <c r="C2" t="n">
-        <v>0.3384250196146384</v>
+        <v>0.3384250196146679</v>
       </c>
       <c r="D2" t="n">
-        <v>1.573643614195673</v>
+        <v>1.573643614195615</v>
       </c>
       <c r="E2" t="n">
-        <v>2.900245314019579</v>
+        <v>2.900245314019636</v>
       </c>
       <c r="F2" t="n">
-        <v>3.846647276144932e-11</v>
+        <v>3.846647276159917e-11</v>
       </c>
       <c r="G2" t="n">
         <v>0.05</v>
@@ -1492,16 +1492,16 @@
         <v>0.181150802664234</v>
       </c>
       <c r="C3" t="n">
-        <v>0.06590363351848991</v>
+        <v>0.06590363351848998</v>
       </c>
       <c r="D3" t="n">
-        <v>0.05198205451766702</v>
+        <v>0.05198205451766694</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3103195508108009</v>
+        <v>0.3103195508108011</v>
       </c>
       <c r="F3" t="n">
-        <v>0.005982800716697901</v>
+        <v>0.005982800716697941</v>
       </c>
       <c r="G3" t="n">
         <v>0.05</v>
@@ -1517,16 +1517,16 @@
         <v>0.2889210511748292</v>
       </c>
       <c r="C4" t="n">
-        <v>0.152598570159998</v>
+        <v>0.1525985701599981</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.01016665043107551</v>
+        <v>-0.01016665043107556</v>
       </c>
       <c r="E4" t="n">
         <v>0.5880087527807341</v>
       </c>
       <c r="F4" t="n">
-        <v>0.05831260422500208</v>
+        <v>0.05831260422500213</v>
       </c>
       <c r="G4" t="n">
         <v>0.05</v>
@@ -1539,19 +1539,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.005957694933862404</v>
+        <v>-0.005957694933862395</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1146433802895678</v>
+        <v>0.1146433802895684</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.2306545913673444</v>
+        <v>-0.2306545913673455</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2187392014996196</v>
+        <v>0.2187392014996207</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9585548324340618</v>
+        <v>0.958554832434062</v>
       </c>
       <c r="G5" t="n">
         <v>0.05</v>
@@ -1564,19 +1564,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.2614273190347506</v>
+        <v>0.2614273190347505</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1392840286028359</v>
+        <v>0.1392840286028366</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.01156436064845456</v>
+        <v>-0.01156436064845606</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5344189987179557</v>
+        <v>0.5344189987179571</v>
       </c>
       <c r="F6" t="n">
-        <v>0.06052675630473976</v>
+        <v>0.06052675630474114</v>
       </c>
       <c r="G6" t="n">
         <v>0.05</v>
@@ -1589,19 +1589,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.01841397076183374</v>
+        <v>-0.01841397076183392</v>
       </c>
       <c r="C7" t="n">
-        <v>0.122319336758662</v>
+        <v>0.1223193367586622</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.2581554654216376</v>
+        <v>-0.2581554654216383</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2213275238979701</v>
+        <v>0.2213275238979704</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8803384800164817</v>
+        <v>0.8803384800164809</v>
       </c>
       <c r="G7" t="n">
         <v>0.05</v>
@@ -1614,19 +1614,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1905247839024714</v>
+        <v>0.1905247839024713</v>
       </c>
       <c r="C8" t="n">
-        <v>0.1312065100950983</v>
+        <v>0.1312065100950985</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.06663525042111218</v>
+        <v>-0.06663525042111285</v>
       </c>
       <c r="E8" t="n">
-        <v>0.447684818226055</v>
+        <v>0.4476848182260554</v>
       </c>
       <c r="F8" t="n">
-        <v>0.146474203287111</v>
+        <v>0.1464742032871121</v>
       </c>
       <c r="G8" t="n">
         <v>0.05</v>
@@ -1639,19 +1639,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1647719700746341</v>
+        <v>0.164771970074634</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1133318732696419</v>
+        <v>0.1133318732696424</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.05735441983432171</v>
+        <v>-0.05735441983432277</v>
       </c>
       <c r="E9" t="n">
-        <v>0.3868983599835899</v>
+        <v>0.3868983599835908</v>
       </c>
       <c r="F9" t="n">
-        <v>0.145977067888413</v>
+        <v>0.1459770678884148</v>
       </c>
       <c r="G9" t="n">
         <v>0.05</v>
@@ -1667,16 +1667,16 @@
         <v>-0.2220479403681949</v>
       </c>
       <c r="C10" t="n">
-        <v>0.1738904480020734</v>
+        <v>0.1738904480020738</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.5628669557077937</v>
+        <v>-0.5628669557077947</v>
       </c>
       <c r="E10" t="n">
-        <v>0.118771074971404</v>
+        <v>0.1187710749714047</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2016228791937926</v>
+        <v>0.2016228791937935</v>
       </c>
       <c r="G10" t="n">
         <v>0.05</v>
@@ -1689,19 +1689,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.03288756718509728</v>
+        <v>0.03288756718509719</v>
       </c>
       <c r="C11" t="n">
-        <v>0.1776097727247108</v>
+        <v>0.1776097727247112</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.3152211906576804</v>
+        <v>-0.3152211906576813</v>
       </c>
       <c r="E11" t="n">
-        <v>0.3809963250278749</v>
+        <v>0.3809963250278756</v>
       </c>
       <c r="F11" t="n">
-        <v>0.8530976171323723</v>
+        <v>0.853097617132373</v>
       </c>
       <c r="G11" t="n">
         <v>0.05</v>
@@ -1714,19 +1714,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-0.01926300923725715</v>
+        <v>-0.01926300923725721</v>
       </c>
       <c r="C12" t="n">
-        <v>0.185793753035985</v>
+        <v>0.1857937530359848</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.3834120737403171</v>
+        <v>-0.3834120737403168</v>
       </c>
       <c r="E12" t="n">
-        <v>0.3448860552658028</v>
+        <v>0.3448860552658023</v>
       </c>
       <c r="F12" t="n">
-        <v>0.917423670738676</v>
+        <v>0.9174236707386756</v>
       </c>
       <c r="G12" t="n">
         <v>0.05</v>
@@ -1742,16 +1742,16 @@
         <v>0.02751012339829574</v>
       </c>
       <c r="C13" t="n">
-        <v>0.1635058900678629</v>
+        <v>0.1635058900678632</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.2929555323948809</v>
+        <v>-0.2929555323948815</v>
       </c>
       <c r="E13" t="n">
-        <v>0.3479757791914724</v>
+        <v>0.347975779191473</v>
       </c>
       <c r="F13" t="n">
-        <v>0.8663853688450225</v>
+        <v>0.8663853688450227</v>
       </c>
       <c r="G13" t="n">
         <v>0.05</v>
@@ -1764,19 +1764,19 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.2140509916498261</v>
+        <v>-0.2140509916498262</v>
       </c>
       <c r="C14" t="n">
         <v>0.1996415110470127</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.6053411631211263</v>
+        <v>-0.6053411631211266</v>
       </c>
       <c r="E14" t="n">
-        <v>0.1772391798214742</v>
+        <v>0.1772391798214741</v>
       </c>
       <c r="F14" t="n">
-        <v>0.2836406395758082</v>
+        <v>0.2836406395758079</v>
       </c>
       <c r="G14" t="n">
         <v>0.05</v>
@@ -1789,19 +1789,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.1171045186779468</v>
+        <v>0.1171045186779469</v>
       </c>
       <c r="C15" t="n">
-        <v>0.1619967599285946</v>
+        <v>0.1619967599285948</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.2004032963942799</v>
+        <v>-0.2004032963942804</v>
       </c>
       <c r="E15" t="n">
-        <v>0.4346123337501736</v>
+        <v>0.4346123337501741</v>
       </c>
       <c r="F15" t="n">
-        <v>0.4697524708434638</v>
+        <v>0.4697524708434644</v>
       </c>
       <c r="G15" t="n">
         <v>0.05</v>
@@ -1814,19 +1814,19 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.01272868241196943</v>
+        <v>-0.0127286824119694</v>
       </c>
       <c r="C16" t="n">
-        <v>0.1645558921490829</v>
+        <v>0.1645558921490834</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.3352523044680294</v>
+        <v>-0.3352523044680304</v>
       </c>
       <c r="E16" t="n">
-        <v>0.3097949396440905</v>
+        <v>0.3097949396440916</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9383437421023137</v>
+        <v>0.9383437421023142</v>
       </c>
       <c r="G16" t="n">
         <v>0.05</v>
@@ -1842,16 +1842,16 @@
         <v>-0.04675708148500214</v>
       </c>
       <c r="C17" t="n">
-        <v>0.1760312745689469</v>
+        <v>0.176031274568947</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.3917720397928196</v>
+        <v>-0.3917720397928198</v>
       </c>
       <c r="E17" t="n">
-        <v>0.2982578768228153</v>
+        <v>0.2982578768228155</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7905333934586961</v>
+        <v>0.7905333934586962</v>
       </c>
       <c r="G17" t="n">
         <v>0.05</v>
@@ -1864,19 +1864,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.0230194693438065</v>
+        <v>-0.02301946934380628</v>
       </c>
       <c r="C18" t="n">
-        <v>0.1644652153812265</v>
+        <v>0.1644652153812268</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.3453653682006333</v>
+        <v>-0.3453653682006337</v>
       </c>
       <c r="E18" t="n">
-        <v>0.2993264295130204</v>
+        <v>0.2993264295130212</v>
       </c>
       <c r="F18" t="n">
-        <v>0.8886871854160932</v>
+        <v>0.8886871854160944</v>
       </c>
       <c r="G18" t="n">
         <v>0.05</v>
@@ -1914,19 +1914,19 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.005402522655627922</v>
+        <v>-0.005402522655627897</v>
       </c>
       <c r="C20" t="n">
-        <v>0.1655922621823108</v>
+        <v>0.1655922621823109</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.329957392651471</v>
+        <v>-0.3299573926514712</v>
       </c>
       <c r="E20" t="n">
-        <v>0.3191523473402152</v>
+        <v>0.3191523473402154</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9739732716462245</v>
+        <v>0.9739732716462246</v>
       </c>
       <c r="G20" t="n">
         <v>0.05</v>
@@ -1939,19 +1939,19 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-0.2427296873564389</v>
+        <v>-0.2427296873564388</v>
       </c>
       <c r="C21" t="n">
-        <v>0.1660896874446663</v>
+        <v>0.1660896874446664</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.5682594929514991</v>
+        <v>-0.5682594929514992</v>
       </c>
       <c r="E21" t="n">
-        <v>0.08280011823862143</v>
+        <v>0.08280011823862174</v>
       </c>
       <c r="F21" t="n">
-        <v>0.1438954327129224</v>
+        <v>0.1438954327129228</v>
       </c>
       <c r="G21" t="n">
         <v>0.05</v>
@@ -1964,7 +1964,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.03768411407691187</v>
+        <v>-0.03768411407691186</v>
       </c>
       <c r="C22" t="n">
         <v>0.1797730666913064</v>
@@ -1989,16 +1989,16 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.02464806102588238</v>
+        <v>-0.02464806102588241</v>
       </c>
       <c r="C23" t="n">
-        <v>0.1900831223009973</v>
+        <v>0.1900831223009976</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.3972041348047595</v>
+        <v>-0.3972041348047601</v>
       </c>
       <c r="E23" t="n">
-        <v>0.3479080127529947</v>
+        <v>0.3479080127529953</v>
       </c>
       <c r="F23" t="n">
         <v>0.8968275912688044</v>
@@ -2014,19 +2014,19 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.205941611377199</v>
+        <v>0.2059416113771989</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0952473837479588</v>
+        <v>0.09524738374795884</v>
       </c>
       <c r="D24" t="n">
-        <v>0.01926016960953411</v>
+        <v>0.01926016960953392</v>
       </c>
       <c r="E24" t="n">
         <v>0.3926230531448639</v>
       </c>
       <c r="F24" t="n">
-        <v>0.03060460934207474</v>
+        <v>0.03060460934207493</v>
       </c>
       <c r="G24" t="n">
         <v>0.05</v>
@@ -2039,19 +2039,19 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.04452008568402004</v>
+        <v>0.04452008568401997</v>
       </c>
       <c r="C25" t="n">
-        <v>0.07833813972634329</v>
+        <v>0.07833813972634333</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.1090198467954792</v>
+        <v>-0.1090198467954794</v>
       </c>
       <c r="E25" t="n">
         <v>0.1980600181635193</v>
       </c>
       <c r="F25" t="n">
-        <v>0.5698267649268587</v>
+        <v>0.5698267649268596</v>
       </c>
       <c r="G25" t="n">
         <v>0.05</v>
@@ -2064,19 +2064,19 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.04831767222516972</v>
+        <v>0.04831767222516932</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1075095082429103</v>
+        <v>0.1075095082429104</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.1623970919265466</v>
+        <v>-0.1623970919265472</v>
       </c>
       <c r="E26" t="n">
-        <v>0.2590324363768861</v>
+        <v>0.2590324363768859</v>
       </c>
       <c r="F26" t="n">
-        <v>0.6531236814450416</v>
+        <v>0.6531236814450445</v>
       </c>
       <c r="G26" t="n">
         <v>0.05</v>
@@ -2089,7 +2089,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.01812015855057374</v>
+        <v>0.01812015855057378</v>
       </c>
       <c r="C27" t="n">
         <v>0.1120508625951185</v>
@@ -2098,10 +2098,10 @@
         <v>-0.2014954965725048</v>
       </c>
       <c r="E27" t="n">
-        <v>0.2377358136736523</v>
+        <v>0.2377358136736524</v>
       </c>
       <c r="F27" t="n">
-        <v>0.8715313227345118</v>
+        <v>0.8715313227345117</v>
       </c>
       <c r="G27" t="n">
         <v>0.05</v>
@@ -2114,19 +2114,19 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.04940558150093542</v>
+        <v>-0.04940558150093539</v>
       </c>
       <c r="C28" t="n">
         <v>0.1079780618094178</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.2610386937678341</v>
+        <v>-0.2610386937678342</v>
       </c>
       <c r="E28" t="n">
-        <v>0.1622275307659633</v>
+        <v>0.1622275307659634</v>
       </c>
       <c r="F28" t="n">
-        <v>0.6472743129266689</v>
+        <v>0.6472743129266691</v>
       </c>
       <c r="G28" t="n">
         <v>0.05</v>
@@ -2139,19 +2139,19 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.04280137104231091</v>
+        <v>0.0428013710423109</v>
       </c>
       <c r="C29" t="n">
         <v>0.1082244098992596</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.169314574608338</v>
+        <v>-0.1693145746083381</v>
       </c>
       <c r="E29" t="n">
-        <v>0.2549173166929598</v>
+        <v>0.2549173166929599</v>
       </c>
       <c r="F29" t="n">
-        <v>0.6924833512519115</v>
+        <v>0.6924833512519117</v>
       </c>
       <c r="G29" t="n">
         <v>0.05</v>
@@ -2164,19 +2164,19 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.4119231277135923</v>
+        <v>0.4119231277135925</v>
       </c>
       <c r="C30" t="n">
-        <v>0.0355166202146675</v>
+        <v>0.03551662021466816</v>
       </c>
       <c r="D30" t="n">
-        <v>0.3423118312402568</v>
+        <v>0.3423118312402556</v>
       </c>
       <c r="E30" t="n">
-        <v>0.4815344241869278</v>
+        <v>0.4815344241869293</v>
       </c>
       <c r="F30" t="n">
-        <v>4.216315028048566e-31</v>
+        <v>4.216315028059068e-31</v>
       </c>
       <c r="G30" t="n">
         <v>0.05</v>
@@ -2185,23 +2185,23 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>tenure_months</t>
+          <t>is_new_manager</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.005696864427362682</v>
+        <v>1.440174177203154</v>
       </c>
       <c r="C31" t="n">
-        <v>0.005018673731113935</v>
+        <v>0.1799506899318473</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.01553328419050325</v>
+        <v>1.087477305943599</v>
       </c>
       <c r="E31" t="n">
-        <v>0.004139555335777885</v>
+        <v>1.792871048462709</v>
       </c>
       <c r="F31" t="n">
-        <v>0.2563194081069056</v>
+        <v>1.212661290946233e-15</v>
       </c>
       <c r="G31" t="n">
         <v>0.05</v>
@@ -2217,16 +2217,16 @@
         <v>-0.01025948591986663</v>
       </c>
       <c r="C32" t="n">
-        <v>0.005466797757691124</v>
+        <v>0.005466797757691274</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.02097421263570556</v>
+        <v>-0.02097421263570586</v>
       </c>
       <c r="E32" t="n">
-        <v>0.0004552407959723011</v>
+        <v>0.000455240795972589</v>
       </c>
       <c r="F32" t="n">
-        <v>0.06056056299802003</v>
+        <v>0.06056056299802699</v>
       </c>
       <c r="G32" t="n">
         <v>0.05</v>
@@ -2235,23 +2235,23 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>baseline_manager_efficacy</t>
+          <t>tenure_months</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.4575134647665858</v>
+        <v>-0.005696864427362678</v>
       </c>
       <c r="C33" t="n">
-        <v>0.04666760652833874</v>
+        <v>0.00501867373111394</v>
       </c>
       <c r="D33" t="n">
-        <v>0.3660466367263556</v>
+        <v>-0.01553328419050326</v>
       </c>
       <c r="E33" t="n">
-        <v>0.548980292806816</v>
+        <v>0.0041395553357779</v>
       </c>
       <c r="F33" t="n">
-        <v>1.085758088206498e-22</v>
+        <v>0.2563194081069063</v>
       </c>
       <c r="G33" t="n">
         <v>0.05</v>
@@ -2267,16 +2267,16 @@
         <v>-0.02794494020865268</v>
       </c>
       <c r="C34" t="n">
-        <v>0.01461262990600847</v>
+        <v>0.01461262990600826</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.05658516854384221</v>
+        <v>-0.05658516854384178</v>
       </c>
       <c r="E34" t="n">
-        <v>0.0006952881265368388</v>
+        <v>0.0006952881265364259</v>
       </c>
       <c r="F34" t="n">
-        <v>0.05582712904150877</v>
+        <v>0.05582712904150519</v>
       </c>
       <c r="G34" t="n">
         <v>0.05</v>
@@ -2285,23 +2285,23 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>is_new_manager</t>
+          <t>tot_span_of_control</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1.440174177203154</v>
+        <v>0.007976972803062379</v>
       </c>
       <c r="C35" t="n">
-        <v>0.1799506899318458</v>
+        <v>0.004378059075285194</v>
       </c>
       <c r="D35" t="n">
-        <v>1.087477305943602</v>
+        <v>-0.0006038653066853337</v>
       </c>
       <c r="E35" t="n">
-        <v>1.792871048462706</v>
+        <v>0.01655781091281009</v>
       </c>
       <c r="F35" t="n">
-        <v>1.212661290945603e-15</v>
+        <v>0.06844981601298375</v>
       </c>
       <c r="G35" t="n">
         <v>0.05</v>
@@ -2310,23 +2310,23 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>tot_span_of_control</t>
+          <t>baseline_manager_efficacy</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.007976972803062383</v>
+        <v>0.4575134647665858</v>
       </c>
       <c r="C36" t="n">
-        <v>0.004378059075285193</v>
+        <v>0.04666760652833871</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.0006038653066853285</v>
+        <v>0.3660466367263556</v>
       </c>
       <c r="E36" t="n">
-        <v>0.01655781091281009</v>
+        <v>0.548980292806816</v>
       </c>
       <c r="F36" t="n">
-        <v>0.06844981601298357</v>
+        <v>1.085758088206443e-22</v>
       </c>
       <c r="G36" t="n">
         <v>0.05</v>
@@ -2375,13 +2375,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-2.680600179802938</v>
+        <v>-2.680600179802939</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4771933030981325</v>
+        <v>0.4771933030981503</v>
       </c>
       <c r="D2" t="n">
-        <v>1.938181768271168e-08</v>
+        <v>1.938181768273511e-08</v>
       </c>
     </row>
     <row r="3">
@@ -2394,7 +2394,7 @@
         <v>-0.02542074333516161</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1002143663033997</v>
+        <v>0.1002143663033998</v>
       </c>
       <c r="D3" t="n">
         <v>0.79975540801217</v>
@@ -2410,10 +2410,10 @@
         <v>0.2244463748843409</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2335027157442914</v>
+        <v>0.2335027157442915</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3364439424069159</v>
+        <v>0.3364439424069162</v>
       </c>
     </row>
     <row r="5">
@@ -2426,10 +2426,10 @@
         <v>0.8155080917228588</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1734026513921177</v>
+        <v>0.173402651392118</v>
       </c>
       <c r="D5" t="n">
-        <v>2.563995828054277e-06</v>
+        <v>2.563995828054386e-06</v>
       </c>
     </row>
     <row r="6">
@@ -2439,13 +2439,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.03527526670387295</v>
+        <v>0.03527526670387308</v>
       </c>
       <c r="C6" t="n">
-        <v>0.191688294691954</v>
+        <v>0.1916882946919544</v>
       </c>
       <c r="D6" t="n">
-        <v>0.853994545471355</v>
+        <v>0.8539945454713548</v>
       </c>
     </row>
     <row r="7">
@@ -2458,10 +2458,10 @@
         <v>0.2773648159307716</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1901447102133382</v>
+        <v>0.1901447102133385</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1446466431125516</v>
+        <v>0.1446466431125523</v>
       </c>
     </row>
     <row r="8">
@@ -2474,10 +2474,10 @@
         <v>0.1036811851537241</v>
       </c>
       <c r="C8" t="n">
-        <v>0.1952515666982443</v>
+        <v>0.1952515666982444</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5954095400432464</v>
+        <v>0.5954095400432469</v>
       </c>
     </row>
     <row r="9">
@@ -2490,10 +2490,10 @@
         <v>0.8738774480300985</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1695280942409136</v>
+        <v>0.1695280942409139</v>
       </c>
       <c r="D9" t="n">
-        <v>2.539495077342701e-07</v>
+        <v>2.539495077342821e-07</v>
       </c>
     </row>
     <row r="10">
@@ -2503,13 +2503,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.04456520772617086</v>
+        <v>-0.0445652077261707</v>
       </c>
       <c r="C10" t="n">
-        <v>0.2604021031716313</v>
+        <v>0.260402103171632</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8641137091517834</v>
+        <v>0.8641137091517843</v>
       </c>
     </row>
     <row r="11">
@@ -2519,13 +2519,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.2737623724798149</v>
+        <v>-0.2737623724798146</v>
       </c>
       <c r="C11" t="n">
-        <v>0.2787881385465057</v>
+        <v>0.2787881385465067</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3261132423877617</v>
+        <v>0.326113242387764</v>
       </c>
     </row>
     <row r="12">
@@ -2535,10 +2535,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.08100487957118127</v>
+        <v>0.08100487957118148</v>
       </c>
       <c r="C12" t="n">
-        <v>0.2596429772097166</v>
+        <v>0.2596429772097172</v>
       </c>
       <c r="D12" t="n">
         <v>0.7550514391424692</v>
@@ -2551,13 +2551,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.03917827337461736</v>
+        <v>0.03917827337461754</v>
       </c>
       <c r="C13" t="n">
-        <v>0.2572958805743769</v>
+        <v>0.2572958805743774</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8789745077123745</v>
+        <v>0.8789745077123743</v>
       </c>
     </row>
     <row r="14">
@@ -2567,13 +2567,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.05296103812307947</v>
+        <v>-0.05296103812307935</v>
       </c>
       <c r="C14" t="n">
-        <v>0.2610089865588713</v>
+        <v>0.2610089865588724</v>
       </c>
       <c r="D14" t="n">
-        <v>0.8392062624375523</v>
+        <v>0.8392062624375534</v>
       </c>
     </row>
     <row r="15">
@@ -2583,13 +2583,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.1181322726534159</v>
+        <v>0.1181322726534161</v>
       </c>
       <c r="C15" t="n">
-        <v>0.2572294350577177</v>
+        <v>0.2572294350577187</v>
       </c>
       <c r="D15" t="n">
-        <v>0.646055612898408</v>
+        <v>0.6460556128984086</v>
       </c>
     </row>
     <row r="16">
@@ -2599,13 +2599,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.004000986240379581</v>
+        <v>-0.004000986240379481</v>
       </c>
       <c r="C16" t="n">
-        <v>0.2383903410311186</v>
+        <v>0.2383903410311192</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9866094604655129</v>
+        <v>0.9866094604655132</v>
       </c>
     </row>
     <row r="17">
@@ -2615,13 +2615,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.1057185310395304</v>
+        <v>0.1057185310395306</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2543340222421748</v>
+        <v>0.2543340222421759</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6776529122567303</v>
+        <v>0.677652912256731</v>
       </c>
     </row>
     <row r="18">
@@ -2631,13 +2631,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.1377694895733256</v>
+        <v>-0.1377694895733254</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2636874203313626</v>
+        <v>0.2636874203313636</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6013412201546261</v>
+        <v>0.6013412201546282</v>
       </c>
     </row>
     <row r="19">
@@ -2647,13 +2647,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-0.02557154094223238</v>
+        <v>-0.02557154094223237</v>
       </c>
       <c r="C19" t="n">
-        <v>0.252759790153811</v>
+        <v>0.2527597901538116</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9194160355966675</v>
+        <v>0.9194160355966677</v>
       </c>
     </row>
     <row r="20">
@@ -2663,13 +2663,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.07344622569376427</v>
+        <v>-0.07344622569376411</v>
       </c>
       <c r="C20" t="n">
-        <v>0.267457860954101</v>
+        <v>0.2674578609541021</v>
       </c>
       <c r="D20" t="n">
-        <v>0.7836169672222772</v>
+        <v>0.7836169672222787</v>
       </c>
     </row>
     <row r="21">
@@ -2679,13 +2679,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.2063167170305059</v>
+        <v>0.2063167170305062</v>
       </c>
       <c r="C21" t="n">
-        <v>0.244289653245072</v>
+        <v>0.2442896532450728</v>
       </c>
       <c r="D21" t="n">
-        <v>0.3983578134719846</v>
+        <v>0.3983578134719854</v>
       </c>
     </row>
     <row r="22">
@@ -2695,13 +2695,13 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.1704634573362026</v>
+        <v>-0.1704634573362028</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2696748454965904</v>
+        <v>0.269674845496591</v>
       </c>
       <c r="D22" t="n">
-        <v>0.5273167196806361</v>
+        <v>0.5273167196806365</v>
       </c>
     </row>
     <row r="23">
@@ -2711,13 +2711,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.5008110927334757</v>
+        <v>-0.5008110927334755</v>
       </c>
       <c r="C23" t="n">
-        <v>0.287067218044571</v>
+        <v>0.2870672180445716</v>
       </c>
       <c r="D23" t="n">
-        <v>0.08105838975171785</v>
+        <v>0.0810583897517186</v>
       </c>
     </row>
     <row r="24">
@@ -2727,13 +2727,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.9366864721074267</v>
+        <v>0.9366864721074268</v>
       </c>
       <c r="C24" t="n">
         <v>0.1483430409733375</v>
       </c>
       <c r="D24" t="n">
-        <v>2.713396260923891e-10</v>
+        <v>2.713396260923871e-10</v>
       </c>
     </row>
     <row r="25">
@@ -2746,10 +2746,10 @@
         <v>-0.5776106069409677</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1143619392421807</v>
+        <v>0.1143619392421806</v>
       </c>
       <c r="D25" t="n">
-        <v>4.401383208103943e-07</v>
+        <v>4.401383208103854e-07</v>
       </c>
     </row>
     <row r="26">
@@ -2759,13 +2759,13 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.237316144844174</v>
+        <v>0.2373161448441742</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1503781926377478</v>
+        <v>0.1503781926377481</v>
       </c>
       <c r="D26" t="n">
-        <v>0.1145360411757813</v>
+        <v>0.1145360411757815</v>
       </c>
     </row>
     <row r="27">
@@ -2775,13 +2775,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.04350476117998651</v>
+        <v>-0.04350476117998643</v>
       </c>
       <c r="C27" t="n">
-        <v>0.1611879340386412</v>
+        <v>0.1611879340386415</v>
       </c>
       <c r="D27" t="n">
-        <v>0.7872365295400213</v>
+        <v>0.7872365295400221</v>
       </c>
     </row>
     <row r="28">
@@ -2791,13 +2791,13 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.07514354096975732</v>
+        <v>-0.07514354096975739</v>
       </c>
       <c r="C28" t="n">
-        <v>0.1613683918223567</v>
+        <v>0.1613683918223571</v>
       </c>
       <c r="D28" t="n">
-        <v>0.6414556246120151</v>
+        <v>0.6414556246120158</v>
       </c>
     </row>
     <row r="29">
@@ -2807,29 +2807,29 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.09749293462742097</v>
+        <v>0.09749293462742094</v>
       </c>
       <c r="C29" t="n">
-        <v>0.1543265796290165</v>
+        <v>0.1543265796290169</v>
       </c>
       <c r="D29" t="n">
-        <v>0.5275624553510008</v>
+        <v>0.5275624553510021</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>tenure_months</t>
+          <t>is_new_manager</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.002418133412192873</v>
+        <v>0.2280638724458788</v>
       </c>
       <c r="C30" t="n">
-        <v>0.007135781003458546</v>
+        <v>0.1146565719927948</v>
       </c>
       <c r="D30" t="n">
-        <v>0.7347043603418277</v>
+        <v>0.04668969945129902</v>
       </c>
     </row>
     <row r="31">
@@ -2839,45 +2839,45 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.005012017390962195</v>
+        <v>-0.005012017390962181</v>
       </c>
       <c r="C31" t="n">
-        <v>0.008304876992455039</v>
+        <v>0.008304876992454899</v>
       </c>
       <c r="D31" t="n">
-        <v>0.5461741835341576</v>
+        <v>0.5461741835341518</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>num_direct_reports</t>
+          <t>tenure_months</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.004129656026475419</v>
+        <v>-0.002418133412192865</v>
       </c>
       <c r="C32" t="n">
-        <v>0.02222260881033174</v>
+        <v>0.007135781003458533</v>
       </c>
       <c r="D32" t="n">
-        <v>0.8525770672961279</v>
+        <v>0.7347043603418282</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>is_new_manager</t>
+          <t>num_direct_reports</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.2280638724458785</v>
+        <v>-0.004129656026475429</v>
       </c>
       <c r="C33" t="n">
-        <v>0.1146565719927948</v>
+        <v>0.02222260881033176</v>
       </c>
       <c r="D33" t="n">
-        <v>0.04668969945129923</v>
+        <v>0.8525770672961277</v>
       </c>
     </row>
     <row r="34">
@@ -2887,13 +2887,13 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.006335499136474495</v>
+        <v>0.006335499136474494</v>
       </c>
       <c r="C34" t="n">
-        <v>0.006871422968197181</v>
+        <v>0.006871422968197173</v>
       </c>
       <c r="D34" t="n">
-        <v>0.3565249957666435</v>
+        <v>0.3565249957666431</v>
       </c>
     </row>
   </sheetData>
